--- a/maclarim.xlsx
+++ b/maclarim.xlsx
@@ -453,12 +453,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Veri Cekilemedi</t>
+          <t>Hala veri yok</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>API anahtarini kontrol et</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/maclarim.xlsx
+++ b/maclarim.xlsx
@@ -453,12 +453,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hala veri yok</t>
+          <t>HATA RAPORU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>API anahtarini kontrol et</t>
+          <t>API bağlandı ama bu lig/sezon için maç bulunamadı.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/maclarim.xlsx
+++ b/maclarim.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,39 +436,4990 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tarih</t>
+          <t>Dakika</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ev</t>
+          <t>Ev Sahibi</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Dep</t>
+          <t>Deplasman</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Skor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HATA RAPORU</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>API bağlandı ama bu lig/sezon için maç bulunamadı.</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FC St. Pauli</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1. FC Köln</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AFC Champions League Elite</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HNL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NK Osijek</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NK Varaždin</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LaLiga 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Real Sociedad B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Real Racing Club</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LaLiga 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Serie B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Le Mans</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Clermont Foot</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Grenoble Foot 38</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Annecy FC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1 - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rodez AF</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Amiens SC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FC Dordrecht</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SC Cambuur</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Helmond Sport</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VVV-Venlo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FC Eindhoven</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Jong PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jong Ajax</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Roda JC Kerkrade</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FC Emmen</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MVV Maastricht</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jong AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Legia Warszawa</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Zagłębie Lubin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Premier Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>St. Patrick's Athletic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0 - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Premier Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Dundalk FC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Galway United</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Premier Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Premier Division</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bohemian FC</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Challenger Pro League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Jong KRC Genk U23</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>KAA Gent Reserve U23</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Challenger Pro League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K. Beerschot V.A.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lommel SK</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Challenger Pro League</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RWDM Brussels</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Challenger Pro League</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Koninklijke Lierse Sportkring</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>KSC Lokeren</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Challenger Pro League</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Patro Eisden Maasmechelen</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Royal Francs Borains</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Challenger Pro League</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RFC Liège</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>KAS Eupen</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Challenger Pro League</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>RFC Seraing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SK Beveren</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Challenger Pro League</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RSCA Futures U23</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OC Charleroi</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NB I</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Újpest</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Nyiregyháza Spartacus</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>International Friendly Games, Women</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Mali</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FA Youth Cup</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Manchester United U18</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Crystal Palace U18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primera Federacion, Group 2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Real Murcia</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Antequera</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Serie D, Group C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AC Este 1920</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Union Clodiense</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>General Lamadrid</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Victoriano Arenas</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Primera C</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sacachispas</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Deportivo Español</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Camp. De Reser De Primera Division B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Berazategui Reserve</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Yupanqui Reserves</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Camp. De Reser De Primera Division B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CA Claypole Reserves</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Victoriano Arenas Reserves</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2. Liga</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Admira Wacker</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>First Vienna FC</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2. Liga</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Young Violets Austria Wien</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Austria Salzburg</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Burgenland 1. Klasse - Mitte</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SV Loipersbach</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SC Dörfl</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Burgenland 1. Klasse - Nord</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UFC Purbach</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SC Wulkaprodersdorf</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Burgenland 1. Klasse - Süd</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SV Großpetersdorf</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ASV Sankt Martin AN Der Raab</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1. Klasse Mitte</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SC Ebner-Trans Machtrenk Juniors</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SPG Wilhering / Mühlbach</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Burgenland Frauen Landesliga</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FC Deutschkreutz</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SPG Sigleß-Neudörfl/Sredina</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>U21 Pro League</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>RFC Seraing Reserve U21</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Royal Charleroi Reserve U23</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>4 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>U21 Pro League</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>RWD Molenbeek Reserve U21</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RFC Liege U21</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>U21 Pro League</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Raal La Louviere U21</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Waasland Beveren Reserve U21</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Derde Afdeling VV B</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FC Wezel Sport</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>KFC Turnhout</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KVDV Zaterdag 1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>De Witte</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>B-Reserven Merksplas</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1 - 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WWIN Liga BiH</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FK Željezničar</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HŠK Posušje</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Brasileirão Série A3, Feminino, Grupo A3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Araguari</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Real HEIPS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Brasileirão Série A3, Feminino, Grupo A4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Mauaense</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>U20 Goiano</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Royal FC U20</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Vila Nova U20</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>U20 Mineiro</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro U20</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Minas Boca Futebol U20</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>10 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>U20 Mineiro</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Coimbra FC Porto U20</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Athletic Club U20</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>U20 Paranaense</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Operário-PR U20</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Galo Maringá U20</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>U17 Goiano</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Santa Cruz-GO U17</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Cristianópolis U17</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>U17 Goiano</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Atlético Goianiense U17</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Canedo FC U17</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>U17 Goiano</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Goiás U17</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Cerrado U17</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>U17 Goiano</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Goiânia U17</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>São Luíz-GO U17</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>U17 Goiano</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Jataiense U17</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Itaberaí U17</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>U17 Goiano</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Vila Nova U17</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Trindade U17</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Northern Premier League, Division One East</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Pontefract Collieries</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Emley AFC</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>U21 Premier League 2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Blackburn U21</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Tottenham U21</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>U21 Premier League 2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Everton U21</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ipswich Town U21</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>6 - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>U21 Premier League 2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Stoke City U21</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Aston Villa U21</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Essex Senior League</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Hackney Wick FC</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sporting Bengal United</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Spartan South Midlands Division One</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Stotfold Reserves</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Letchworth Garden City Eagles</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Combined Counties League Premier Division North</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Reading City FC</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Abingdon United</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Essex Senior Football League, Reserve Division</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Hutton Under 23</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Takeley Reserves</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Go2Day West Cheshire AF League</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>FC Bootle</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Chester Nomads</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Southern Counties East League Premier Division</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Erith &amp; Belvedere FC</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Phoenix Sports FC</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Northern League - Division One</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Newcastle Blue Star FC</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>North Shields</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Northern League - Division One</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Northallerton Town FC</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Horden Community Welfare</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Stranger Charity Cup, Knockout</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>St. Martin's AC</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Belgrave Wanderers FC</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Somerset County League Premier Division</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fry Club FC</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Stockwood Green FC</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>II Liiga - A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Paide Linnameeskond U21</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Harju Jalgpallikool U21</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>5 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>II Liiga - B</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ida-Viru JK Noova</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>FC Elva U21</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>III Liiga - Põhi-Lääs piirkond</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Viimsi Lõvid</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Märjamaa Kompanii</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Nelonen, Eteläinen - Lohko 1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EPS/I</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Bollklubben 1946</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Naisten Nelonen, Eteläinen, Kevät 1</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>EPS/N</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ekenäs IF</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Auvergne Rhône-Alpes, Regional A</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Montluçon Football</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>GOAL FC B</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Bremen-Liga</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Leher TS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>KSV Vatan Sport</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Oberliga Niederrhein</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>VfL Jüchen-Garzweiler</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TSV Meerbusch</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Berlin Verbandsliga</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1. FC Wilmersdorf</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Frohnauer SC</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Berlin Verbandsliga</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Füchse Berlin Reinickendorf</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SV BW Hohen Neuendorf</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Berlin Verbandsliga</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SC Charlottenburg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SC Staaken</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Landesliga Hammonia</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FC St. Pauli III</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>TUS Osdorf</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Landesliga Hammonia</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Hamburger SV III</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>TBS Pinneberg</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Landesliga Hammonia</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SC Nienstedten</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Union Tornesch</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Gruppenliga Kassel - Gruppe 1</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TSV Altenlotheim</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SG Brunslar/Wolfershausen</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Kreisliga C Rhein-Lahn</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SG Mühlbachtal Oelsberg III</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>TuS Singhofen II</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>5 - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Kreisliga A Düsseldorf</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SC Düsseldorf West</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SC Unterbach</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Landesliga Brandenburg, Sud</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SV Frankonia Wernsdorf</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VfB 1921 Krieschow II</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Landesliga Brandenburg, Sud</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SV Victoria Seelow</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SG Großziethen</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>6 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Kreisliga A Maintaunus</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FV Alemannia Nied II</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Germania Weilbach  II</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Landesliga Lüneburg</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TSV Ottersberg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Rotenburger SV</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Landesliga Südost - Bayern</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TSV Grünwald</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VfB Hallbergmoos</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Landesliga Südost - Bayern</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Eintracht Karlsfeld</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>FC Wacker München</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Kreisliga Oberhavel/Barnim, Ost</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1. FC Finowfurt</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1.FV Eintracht Wandlitz II</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Kreisliga Oberhavel/Barnim, Ost</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>FSV Lok Eberswalde</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BSV Blumberg</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Kreisliga Südbrandenburg, Ost</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SV Blau-Weiß Lubolz</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>FSV Groß-Leuthen/​Gröditsch</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>C-Klasse München 1</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TSV Indersdorf III</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>TSV Eintracht Karlsfeld IV</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Landesliga Niederrhein, Gruppe 1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SG Unterrath</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SC Velbert</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>3 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Landesliga Niederrhein, Gruppe 1</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SC Victoria Mennrath</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Spvg. Solingen-Wald</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Landesliga Berlin, Group B</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>FC Stern Marienfelde</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>FSV Berolina Stralau</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Landesliga Berlin, Group B</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BFC Meteor 06</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>FV Wannsee</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kreisliga C Recklinghausen, Group 1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Sportfreunde Nordvelen 1976 e.V.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Adler Weseke II</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>U19 Kreisliga Darmstadt/Bergstraße/Groß-Gerau</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SV Weiterstadt U19</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>JFV Bürstadt U19</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>U17 Kreisliga A Bergstraße</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SV Fürth U17</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>JSG Reichenbach/​Nibelungen U17</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Larissa Liga</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Panthers</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2 - 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Efsta deild</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Breidablik Kópavogur</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ÍA Akranes</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Efsta deild</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Fram Reykjavík</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Keflavík IF</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Icelandic Men's Football League Cup C, Group 1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Arborg</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Uppsveitir</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>First Division</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Athlone Town AFC</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>First Division</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers FC</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Longford Town</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>First Division</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Wexford FC</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>First Division</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Kerry FC</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Treaty United FC</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>First Division</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>University College Dublin</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Leinster Senior League Senior Division</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Inchicore Athletic FC</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Ballymun United</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Terza Categoria Calabria - Girone D</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>A.S.D. Centro Storico Catanzaro</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>A.S.D. Grifone Catanzaro</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Terza Categoria Alto Adige, Girone B</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AC.SG Sciliar Schlern B</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>F.C. Neumarkt Egna</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Terza Categoria Alto Adige, Girone C</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SG Latzfons Verdings B</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>S.C. Rasen A.S.D.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Final Stage - Playoff</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Masseria Vero</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Boca Junior</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BOV Amateur League I</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Senglea Athletic FC</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Luqa St. Andrew's FC</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>GFA 1st Division KO - 1st Knockout</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>S.K. Victoria Wanderers</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Kercem Ajax F.C.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Mexico U19 League, Clausura</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Atletico San Luis U19</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Pumas UNAM U19</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>3 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Mexico U19 League, Clausura</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mazatlán FC U19</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Querétaro Gallos Blancos U19</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Premiership, Championship Round</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Glentoran FC</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Larne FC</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>NIFL Women's Premiership League Cup, Group B</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Derry City Women</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Cliftonville LFC</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0 - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>NIFL Premier Intermediate League</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Newry City AFC</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Strabane Athletic FC</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>I liga</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Stal Rzeszów</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Polonia Warszawa</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Liga Okręgowa - Warszawa II</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>GKS Podolszyn</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Korona Góra Kalwaria</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Klasa A - Podlaska, Group 2</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Hattrick Białystok</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Włókniarz Białystok</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Klasa A - Łódzka II</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Teofilek Łódź</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LKS Kwiatkowice</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Liga Portugal 2</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Académico Viseu FC</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Feirense</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>3 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Liga 4 Harghita</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CS Roseal Odorheiu Secuiesc</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CS Metalul Vlăhița</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2nd SNL</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NK Tabor Sežana</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NK Nafta Lendava 1903</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Tercera Federación Femenina, Grupo 4</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Añorga KKE</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Bilbao Artizarrak FK</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Division 3 Södra Norrland</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>IK Huge</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Avesta AIK</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Division 4 Uppland</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Rosersbergs IK</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Håbo FF</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Division 5 Uppland, Västra</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Vattholma IF</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>IFK Uppsala 2</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Division 4 Södermanland</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Högsjö BK</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Oxelösunds IK</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Challenge League</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Étoile Carouge FC</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>FC Wil 1900</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2. Liga AFV</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FC Neuenhof</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>FC Spreitenbach</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2. Liga AFV</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>FC Wohlen 2</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>FC Muri</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2a. Lega FTC</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>FC Moderna</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AS Monteceneri</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>3a. Lega FTC - Gruppo 1</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AS Coldrerio</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>FC Origlio-Ponte Capriasca</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>3a. Lega FTC - Gruppo 1</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>FC Riva</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>FC Stella Capriasca</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>3a. Lega FTC - Gruppo 2</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AC Arbedo-Castione</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Moesano Calcio</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>3a. Lega FTC - Gruppo 2</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>FC Intragna</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>GC Carassesi</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>3a. Lega FTC - Gruppo 2</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>US Giubiasco</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>FC Makedonija Locarno</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>4a. Lega FTC - Gruppo 1</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ASM Arzo</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CO Boglia Cadro</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>4a. Lega FTC - Gruppo 1</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FC Insubrica</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>AS Novazzano 2</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4a. Lega FTC - Gruppo 2</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FC Savosa-Massagno</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>FC Rapid Bironico</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>3 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>4a. Lega FTC - Gruppo 3</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>FC Camorino</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>US Chironico</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>4a. Lega FTC - Gruppo 4</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>FC Aramaici-Suryoye</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>FC Someo</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>4a. Lega FTC - Gruppo 4</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>FC Pedemonte</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>AC Codeborgo-Artore</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2. Liga OFV - Gruppe 2</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FC Bazenheid</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>FC Bütschwil</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>4. Liga SOFV - Gruppe 2</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FC Däniken-Gretzenbach II</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>FC Winznau II</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>3e Ligue AVF/3. Liga WFV - Groupe/Gruppe 1</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>FC Leuk-Susten</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>FC St. Niklaus</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>FC Agarn Turtmann</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>FC Brig-Glis 3</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>FC Region Goms</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>FC St. Niklaus 2</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>FC Termen/Ried-Brig 2</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>FC Saas Fee</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 3</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>FC Lens Chermignon 2</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>FC Ardon 2</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 4</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>FC Bagnes-Vollèges 2</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>FC Evionnaz-Collonges</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 4</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>FC Vernayaz 2</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>FC Orsières 2 Liddes</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>5e Ligue AVF/5. Liga WFV - Groupe 1</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>FC Anniviers</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>US Ayent-Arbaz 2</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>5e Ligue AVF/5. Liga WFV - Groupe 2</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>FC Chamoson 2</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>FC Fully 3</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Frauen 2. Liga</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Started</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>FC Niederlenz</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>FC Therwil Frauen 1</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Pozitif Lig, Group B</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tıktık Spor</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Esenler FC</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Pozitiflig Güney, Group B</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Teletabiler FK</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Liberty City</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2 - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Futbolig Açılış Sezonu, Group B</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1st half</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Farketmez FK</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Ardal Leagues, South West</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Penrhiwceiber Rangers</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Pure Swansea FC</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Ardal Leagues, South West</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Evans &amp; Williams AFC</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Ynysygerwyn FC</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>1 - 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Ardal Leagues, South East</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2nd half</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Goytre FC</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Caerphilly Athletic FC</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>1 - 1</t>
         </is>
       </c>
     </row>

--- a/maclarim.xlsx
+++ b/maclarim.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Dakika</t>
+          <t>Tarih</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4 - 0</t>
+          <t>5 - 0</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1st half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>1 - 1</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0 - 2</t>
+          <t>0 - 3</t>
         </is>
       </c>
     </row>
@@ -3298,49 +3298,49 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TSV Grünwald</t>
+          <t>Eintracht Karlsfeld</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VfB Hallbergmoos</t>
+          <t>FC Wacker München</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2 - 0</t>
+          <t>0 - 1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Landesliga Südost - Bayern</t>
+          <t>Kreisliga Oberhavel/Barnim, Ost</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eintracht Karlsfeld</t>
+          <t>1. FC Finowfurt</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>FC Wacker München</t>
+          <t>1.FV Eintracht Wandlitz II</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0 - 1</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1. FC Finowfurt</t>
+          <t>FSV Lok Eberswalde</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1.FV Eintracht Wandlitz II</t>
+          <t>BSV Blumberg</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3374,7 +3374,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Kreisliga Oberhavel/Barnim, Ost</t>
+          <t>Kreisliga Südbrandenburg, Ost</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FSV Lok Eberswalde</t>
+          <t>SV Blau-Weiß Lubolz</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BSV Blumberg</t>
+          <t>FSV Groß-Leuthen/​Gröditsch</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3401,7 +3401,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kreisliga Südbrandenburg, Ost</t>
+          <t>C-Klasse München 1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SV Blau-Weiß Lubolz</t>
+          <t>TSV Indersdorf III</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FSV Groß-Leuthen/​Gröditsch</t>
+          <t>TSV Eintracht Karlsfeld IV</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3428,27 +3428,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C-Klasse München 1</t>
+          <t>Landesliga Niederrhein, Gruppe 1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TSV Indersdorf III</t>
+          <t>SG Unterrath</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>TSV Eintracht Karlsfeld IV</t>
+          <t>SC Velbert</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>3 - 2</t>
         </is>
       </c>
     </row>
@@ -3465,44 +3465,44 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SG Unterrath</t>
+          <t>SC Victoria Mennrath</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SC Velbert</t>
+          <t>Spvg. Solingen-Wald</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3 - 2</t>
+          <t>1 - 1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Landesliga Niederrhein, Gruppe 1</t>
+          <t>Landesliga Berlin, Group B</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SC Victoria Mennrath</t>
+          <t>FC Stern Marienfelde</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Spvg. Solingen-Wald</t>
+          <t>FSV Berolina Stralau</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1 - 1</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FC Stern Marienfelde</t>
+          <t>BFC Meteor 06</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>FSV Berolina Stralau</t>
+          <t>FV Wannsee</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3536,7 +3536,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Landesliga Berlin, Group B</t>
+          <t>Kreisliga C Recklinghausen, Group 1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BFC Meteor 06</t>
+          <t>Sportfreunde Nordvelen 1976 e.V.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>FV Wannsee</t>
+          <t>Adler Weseke II</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3563,7 +3563,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kreisliga C Recklinghausen, Group 1</t>
+          <t>U19 Kreisliga Darmstadt/Bergstraße/Groß-Gerau</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sportfreunde Nordvelen 1976 e.V.</t>
+          <t>SV Weiterstadt U19</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Adler Weseke II</t>
+          <t>JFV Bürstadt U19</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>U19 Kreisliga Darmstadt/Bergstraße/Groß-Gerau</t>
+          <t>U17 Kreisliga A Bergstraße</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SV Weiterstadt U19</t>
+          <t>SV Fürth U17</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>JFV Bürstadt U19</t>
+          <t>JSG Reichenbach/​Nibelungen U17</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3617,54 +3617,54 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>U17 Kreisliga A Bergstraße</t>
+          <t>Larissa Liga</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>1st half</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SV Fürth U17</t>
+          <t>Panthers</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>JSG Reichenbach/​Nibelungen U17</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>2 - 6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Larissa Liga</t>
+          <t>Efsta deild</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1st half</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Panthers</t>
+          <t>Breidablik Kópavogur</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>ÍA Akranes</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2 - 6</t>
+          <t>1 - 0</t>
         </is>
       </c>
     </row>
@@ -3681,71 +3681,71 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Breidablik Kópavogur</t>
+          <t>Fram Reykjavík</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ÍA Akranes</t>
+          <t>Keflavík IF</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1 - 0</t>
+          <t>2 - 1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Efsta deild</t>
+          <t>Icelandic Men's Football League Cup C, Group 1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>1st half</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fram Reykjavík</t>
+          <t>Arborg</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Keflavík IF</t>
+          <t>Uppsveitir</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Icelandic Men's Football League Cup C, Group 1</t>
+          <t>First Division</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1st half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Arborg</t>
+          <t>Athlone Town AFC</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Uppsveitir</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>1 - 0</t>
         </is>
       </c>
     </row>
@@ -3762,17 +3762,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Athlone Town AFC</t>
+          <t>Cobh Ramblers FC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1 - 0</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cobh Ramblers FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford FC</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>1 - 1</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Wexford FC</t>
+          <t>Treaty United FC</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1 - 1</t>
+          <t>0 - 1</t>
         </is>
       </c>
     </row>
@@ -3843,39 +3843,39 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>University College Dublin</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Treaty United FC</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>0 - 1</t>
+          <t>1 - 0</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>First Division</t>
+          <t>Leinster Senior League Senior Division</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1st half</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>University College Dublin</t>
+          <t>Inchicore Athletic FC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Ballymun United</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3887,34 +3887,34 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Leinster Senior League Senior Division</t>
+          <t>Terza Categoria Calabria - Girone D</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1st half</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Inchicore Athletic FC</t>
+          <t>A.S.D. Centro Storico Catanzaro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ballymun United</t>
+          <t>A.S.D. Grifone Catanzaro</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1 - 0</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Terza Categoria Calabria - Girone D</t>
+          <t>Terza Categoria Alto Adige, Girone B</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>A.S.D. Centro Storico Catanzaro</t>
+          <t>AC.SG Sciliar Schlern B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>A.S.D. Grifone Catanzaro</t>
+          <t>F.C. Neumarkt Egna</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3941,7 +3941,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Terza Categoria Alto Adige, Girone B</t>
+          <t>Terza Categoria Alto Adige, Girone C</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AC.SG Sciliar Schlern B</t>
+          <t>SG Latzfons Verdings B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>F.C. Neumarkt Egna</t>
+          <t>S.C. Rasen A.S.D.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3968,142 +3968,142 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Terza Categoria Alto Adige, Girone C</t>
+          <t>Final Stage - Playoff</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>1st half</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SG Latzfons Verdings B</t>
+          <t>Masseria Vero</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>S.C. Rasen A.S.D.</t>
+          <t>Boca Junior</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>2 - 0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Final Stage - Playoff</t>
+          <t>BOV Amateur League I</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1st half</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Masseria Vero</t>
+          <t>Senglea Athletic FC</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Boca Junior</t>
+          <t>Luqa St. Andrew's FC</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1 - 0</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BOV Amateur League I</t>
+          <t>GFA 1st Division KO - 1st Knockout</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Senglea Athletic FC</t>
+          <t>S.K. Victoria Wanderers</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Luqa St. Andrew's FC</t>
+          <t>Kercem Ajax F.C.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>0 - 1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GFA 1st Division KO - 1st Knockout</t>
+          <t>Mexico U19 League, Clausura</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>S.K. Victoria Wanderers</t>
+          <t>Mazatlán FC U19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Kercem Ajax F.C.</t>
+          <t>Querétaro Gallos Blancos U19</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0 - 1</t>
+          <t>1 - 1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Mexico U19 League, Clausura</t>
+          <t>Premiership, Championship Round</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Atletico San Luis U19</t>
+          <t>Glentoran FC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Pumas UNAM U19</t>
+          <t>Larne FC</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>3 - 2</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mexico U19 League, Clausura</t>
+          <t>NIFL Women's Premiership League Cup, Group B</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4113,39 +4113,39 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mazatlán FC U19</t>
+          <t>Derry City Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Querétaro Gallos Blancos U19</t>
+          <t>Cliftonville LFC</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1 - 1</t>
+          <t>0 - 3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Premiership, Championship Round</t>
+          <t>NIFL Premier Intermediate League</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Glentoran FC</t>
+          <t>Newry City AFC</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Larne FC</t>
+          <t>Strabane Athletic FC</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4157,34 +4157,34 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NIFL Women's Premiership League Cup, Group B</t>
+          <t>I liga</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Derry City Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cliftonville LFC</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0 - 3</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NIFL Premier Intermediate League</t>
+          <t>Liga Okręgowa - Warszawa II</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Newry City AFC</t>
+          <t>GKS Podolszyn</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Strabane Athletic FC</t>
+          <t>Korona Góra Kalwaria</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4211,22 +4211,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>I liga</t>
+          <t>Klasa A - Podlaska, Group 2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Hattrick Białystok</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Włókniarz Białystok</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4238,7 +4238,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Liga Okręgowa - Warszawa II</t>
+          <t>Klasa A - Łódzka II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GKS Podolszyn</t>
+          <t>Teofilek Łódź</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Korona Góra Kalwaria</t>
+          <t>LKS Kwiatkowice</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4265,7 +4265,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Klasa A - Podlaska, Group 2</t>
+          <t>Liga 4 Harghita</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hattrick Białystok</t>
+          <t>CS Roseal Odorheiu Secuiesc</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Włókniarz Białystok</t>
+          <t>CS Metalul Vlăhița</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4292,34 +4292,34 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Klasa A - Łódzka II</t>
+          <t>2nd SNL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Teofilek Łódź</t>
+          <t>NK Tabor Sežana</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LKS Kwiatkowice</t>
+          <t>NK Nafta Lendava 1903</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>0 - 2</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Liga Portugal 2</t>
+          <t>Tercera Federación Femenina, Grupo 4</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4329,24 +4329,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Académico Viseu FC</t>
+          <t>Añorga KKE</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Bilbao Artizarrak FK</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>3 - 0</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Liga 4 Harghita</t>
+          <t>Division 3 Södra Norrland</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CS Roseal Odorheiu Secuiesc</t>
+          <t>IK Huge</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>CS Metalul Vlăhița</t>
+          <t>Avesta AIK</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4373,49 +4373,49 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2nd SNL</t>
+          <t>Division 4 Uppland</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NK Tabor Sežana</t>
+          <t>Rosersbergs IK</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NK Nafta Lendava 1903</t>
+          <t>Håbo FF</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0 - 2</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tercera Federación Femenina, Grupo 4</t>
+          <t>Division 5 Uppland, Västra</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Añorga KKE</t>
+          <t>Vattholma IF</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Bilbao Artizarrak FK</t>
+          <t>IFK Uppsala 2</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4427,7 +4427,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Division 3 Södra Norrland</t>
+          <t>Division 4 Södermanland</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>IK Huge</t>
+          <t>Högsjö BK</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Avesta AIK</t>
+          <t>Oxelösunds IK</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4454,34 +4454,34 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Division 4 Uppland</t>
+          <t>Challenge League</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Rosersbergs IK</t>
+          <t>Étoile Carouge FC</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Håbo FF</t>
+          <t>FC Wil 1900</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>2 - 0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Division 5 Uppland, Västra</t>
+          <t>2. Liga AFV</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Vattholma IF</t>
+          <t>FC Neuenhof</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>IFK Uppsala 2</t>
+          <t>FC Spreitenbach</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4508,7 +4508,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Division 4 Södermanland</t>
+          <t>2. Liga AFV</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Högsjö BK</t>
+          <t>FC Wohlen 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Oxelösunds IK</t>
+          <t>FC Muri</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4535,34 +4535,34 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Challenge League</t>
+          <t>2a. Lega FTC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2nd half</t>
+          <t>Started</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Étoile Carouge FC</t>
+          <t>FC Moderna</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>FC Wil 1900</t>
+          <t>AS Monteceneri</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2 - 0</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2. Liga AFV</t>
+          <t>3a. Lega FTC - Gruppo 1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FC Neuenhof</t>
+          <t>AS Coldrerio</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>FC Spreitenbach</t>
+          <t>FC Origlio-Ponte Capriasca</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4589,7 +4589,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2. Liga AFV</t>
+          <t>3a. Lega FTC - Gruppo 1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FC Wohlen 2</t>
+          <t>FC Riva</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>FC Muri</t>
+          <t>FC Stella Capriasca</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2a. Lega FTC</t>
+          <t>3a. Lega FTC - Gruppo 2</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FC Moderna</t>
+          <t>AC Arbedo-Castione</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>AS Monteceneri</t>
+          <t>Moesano Calcio</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4643,7 +4643,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3a. Lega FTC - Gruppo 1</t>
+          <t>3a. Lega FTC - Gruppo 2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AS Coldrerio</t>
+          <t>FC Intragna</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>FC Origlio-Ponte Capriasca</t>
+          <t>GC Carassesi</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4670,7 +4670,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3a. Lega FTC - Gruppo 1</t>
+          <t>3a. Lega FTC - Gruppo 2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FC Riva</t>
+          <t>US Giubiasco</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>FC Stella Capriasca</t>
+          <t>FC Makedonija Locarno</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4697,7 +4697,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3a. Lega FTC - Gruppo 2</t>
+          <t>4a. Lega FTC - Gruppo 1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AC Arbedo-Castione</t>
+          <t>ASM Arzo</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Moesano Calcio</t>
+          <t>CO Boglia Cadro</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4724,7 +4724,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3a. Lega FTC - Gruppo 2</t>
+          <t>4a. Lega FTC - Gruppo 1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FC Intragna</t>
+          <t>FC Insubrica</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>GC Carassesi</t>
+          <t>AS Novazzano 2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4751,7 +4751,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3a. Lega FTC - Gruppo 2</t>
+          <t>4a. Lega FTC - Gruppo 2</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4761,24 +4761,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>US Giubiasco</t>
+          <t>FC Savosa-Massagno</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>FC Makedonija Locarno</t>
+          <t>FC Rapid Bironico</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>3 - 2</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4a. Lega FTC - Gruppo 1</t>
+          <t>4a. Lega FTC - Gruppo 3</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ASM Arzo</t>
+          <t>FC Camorino</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>CO Boglia Cadro</t>
+          <t>US Chironico</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4a. Lega FTC - Gruppo 1</t>
+          <t>4a. Lega FTC - Gruppo 4</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FC Insubrica</t>
+          <t>FC Aramaici-Suryoye</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>AS Novazzano 2</t>
+          <t>FC Someo</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4832,7 +4832,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4a. Lega FTC - Gruppo 2</t>
+          <t>4a. Lega FTC - Gruppo 4</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4842,24 +4842,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FC Savosa-Massagno</t>
+          <t>FC Pedemonte</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>FC Rapid Bironico</t>
+          <t>AC Codeborgo-Artore</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>3 - 2</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4a. Lega FTC - Gruppo 3</t>
+          <t>2. Liga OFV - Gruppe 2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4869,24 +4869,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FC Camorino</t>
+          <t>FC Bazenheid</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>US Chironico</t>
+          <t>FC Bütschwil</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>0 - 1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4a. Lega FTC - Gruppo 4</t>
+          <t>4. Liga SOFV - Gruppe 2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FC Aramaici-Suryoye</t>
+          <t>FC Däniken-Gretzenbach II</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>FC Someo</t>
+          <t>FC Winznau II</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4a. Lega FTC - Gruppo 4</t>
+          <t>3e Ligue AVF/3. Liga WFV - Groupe/Gruppe 1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FC Pedemonte</t>
+          <t>FC Leuk-Susten</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>AC Codeborgo-Artore</t>
+          <t>FC St. Niklaus</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4940,7 +4940,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2. Liga OFV - Gruppe 2</t>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4950,24 +4950,24 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FC Bazenheid</t>
+          <t>FC Agarn Turtmann</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>FC Bütschwil</t>
+          <t>FC Brig-Glis 3</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0 - 1</t>
+          <t>0 - 0</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4. Liga SOFV - Gruppe 2</t>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FC Däniken-Gretzenbach II</t>
+          <t>FC Region Goms</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>FC Winznau II</t>
+          <t>FC St. Niklaus 2</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4994,7 +4994,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3e Ligue AVF/3. Liga WFV - Groupe/Gruppe 1</t>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FC Leuk-Susten</t>
+          <t>FC Termen/Ried-Brig 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>FC St. Niklaus</t>
+          <t>FC Saas Fee</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5021,7 +5021,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 3</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FC Agarn Turtmann</t>
+          <t>FC Lens Chermignon 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>FC Brig-Glis 3</t>
+          <t>FC Ardon 2</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5048,7 +5048,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 4</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FC Region Goms</t>
+          <t>FC Bagnes-Vollèges 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>FC St. Niklaus 2</t>
+          <t>FC Evionnaz-Collonges</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5075,7 +5075,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4e Ligue AVF/4. Liga WFV - Groupe 1</t>
+          <t>4e Ligue AVF/4. Liga WFV - Groupe 4</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>FC Termen/Ried-Brig 2</t>
+          <t>FC Vernayaz 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>FC Saas Fee</t>
+          <t>FC Orsières 2 Liddes</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5102,7 +5102,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4e Ligue AVF/4. Liga WFV - Groupe 3</t>
+          <t>5e Ligue AVF/5. Liga WFV - Groupe 1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>FC Lens Chermignon 2</t>
+          <t>FC Anniviers</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>FC Ardon 2</t>
+          <t>US Ayent-Arbaz 2</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4e Ligue AVF/4. Liga WFV - Groupe 4</t>
+          <t>5e Ligue AVF/5. Liga WFV - Groupe 2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FC Bagnes-Vollèges 2</t>
+          <t>FC Chamoson 2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>FC Evionnaz-Collonges</t>
+          <t>FC Fully 3</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5156,7 +5156,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4e Ligue AVF/4. Liga WFV - Groupe 4</t>
+          <t>Frauen 2. Liga</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>FC Vernayaz 2</t>
+          <t>FC Niederlenz</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>FC Orsières 2 Liddes</t>
+          <t>FC Therwil Frauen 1</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5183,22 +5183,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5e Ligue AVF/5. Liga WFV - Groupe 1</t>
+          <t>Pozitif Lig, Group B</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>1st half</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>FC Anniviers</t>
+          <t>Tıktık Spor</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>US Ayent-Arbaz 2</t>
+          <t>Esenler FC</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5210,88 +5210,88 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5e Ligue AVF/5. Liga WFV - Groupe 2</t>
+          <t>Pozitiflig Güney, Group B</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FC Chamoson 2</t>
+          <t>Teletabiler FK</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>FC Fully 3</t>
+          <t>Liberty City</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>2 - 1</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Frauen 2. Liga</t>
+          <t>Futbolig Açılış Sezonu, Group B</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>1st half</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>FC Niederlenz</t>
+          <t>Air Force</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>FC Therwil Frauen 1</t>
+          <t>Farketmez FK</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>2 - 0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Pozitif Lig, Group B</t>
+          <t>Ardal Leagues, South West</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1st half</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tıktık Spor</t>
+          <t>Penrhiwceiber Rangers</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Esenler FC</t>
+          <t>Pure Swansea FC</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0 - 0</t>
+          <t>2 - 0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Pozitiflig Güney, Group B</t>
+          <t>Ardal Leagues, South West</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5301,123 +5301,42 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Teletabiler FK</t>
+          <t>Evans &amp; Williams AFC</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Liberty City</t>
+          <t>Ynysygerwyn FC</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>1 - 1</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Futbolig Açılış Sezonu, Group B</t>
+          <t>Ardal Leagues, South East</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1st half</t>
+          <t>2nd half</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Air Force</t>
+          <t>Goytre FC</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Farketmez FK</t>
+          <t>Caerphilly Athletic FC</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
-        <is>
-          <t>2 - 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Ardal Leagues, South West</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2nd half</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Penrhiwceiber Rangers</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Pure Swansea FC</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>2 - 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Ardal Leagues, South West</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2nd half</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Evans &amp; Williams AFC</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Ynysygerwyn FC</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>1 - 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Ardal Leagues, South East</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>2nd half</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Goytre FC</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Caerphilly Athletic FC</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
         <is>
           <t>1 - 1</t>
         </is>

--- a/maclarim.xlsx
+++ b/maclarim.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.04.2026</t>
+          <t>18.04.2026 20:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Örnek Takım A</t>
+          <t>Ev Sahibi Takım</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Örnek Takım B</t>
+          <t>Deplasman Takım</t>
         </is>
       </c>
     </row>
@@ -480,17 +480,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17.04.2026</t>
+          <t>18.04.2026 20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Örnek Takım A</t>
+          <t>Ev Sahibi Takım</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Örnek Takım B</t>
+          <t>Deplasman Takım</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17.04.2026</t>
+          <t>18.04.2026 20:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Örnek Takım A</t>
+          <t>Ev Sahibi Takım</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Örnek Takım B</t>
+          <t>Deplasman Takım</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.04.2026</t>
+          <t>18.04.2026 20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Örnek Takım A</t>
+          <t>Ev Sahibi Takım</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Örnek Takım B</t>
+          <t>Deplasman Takım</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,1007 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17.04.2026</t>
+          <t>18.04.2026 20:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Örnek Takım A</t>
+          <t>Ev Sahibi Takım</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Örnek Takım B</t>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>19.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>19.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>25.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>25.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>25.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>26.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>26.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>26.04.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>02.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>02.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>02.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>02.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>02.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>03.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>03.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>03.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>03.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>03.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>09.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>09.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>09.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>16.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>16.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>16.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>16.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>17.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>17.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>17.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>17.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Trendyol Süper Lig</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>17.05.2026 20:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ev Sahibi Takım</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Deplasman Takım</t>
         </is>
       </c>
     </row>

--- a/maclarim.xlsx
+++ b/maclarim.xlsx
@@ -463,12 +463,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Man City</t>
         </is>
       </c>
     </row>
@@ -485,12 +485,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Milan</t>
         </is>
       </c>
     </row>
@@ -507,12 +507,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Dortmund</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Barcelona</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Chelsea</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Leipzig</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Atletico</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Girona</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Man City</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Milan</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Dortmund</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Barcelona</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Chelsea</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Leipzig</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Atletico</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Girona</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Man City</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Milan</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Dortmund</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Barcelona</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Chelsea</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Leipzig</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Atletico</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Girona</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Man City</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Milan</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Dortmund</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Barcelona</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Chelsea</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Leipzig</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Atletico</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Girona</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Man City</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Milan</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Dortmund</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Barcelona</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Chelsea</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Leipzig</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Atletico</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Girona</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ev Sahibi Takım</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Deplasman Takım</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
     </row>
